--- a/models/8001_DCF_Model_20260906.xlsx
+++ b/models/8001_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF517B7-2EDD-4260-9CD4-C2B2BCDED8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54306A9-3AB2-4E51-B910-4BDCBF2CF4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="354">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -87,10 +87,13 @@
     <t>DCF - Exit Multiple</t>
   </si>
   <si>
+    <t>コアDCF 1株値（フロア規則: 負または不成立なら 0）</t>
+  </si>
+  <si>
     <t>持分法投資価値 [1株・別途加算]</t>
   </si>
   <si>
-    <t>Comps - EV/EBITDA Median [参考・Target不算入]</t>
+    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型F: EV倍率は持分法混在で歪むため不使用）</t>
   </si>
   <si>
     <t>Comps - PER Median [参考・Target不算入]</t>
@@ -760,7 +763,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 02:17, template rev 15b64f7</t>
+    <t>Generated by pipeline on 2026-09-07 11:56, template rev 42941f3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -970,7 +973,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 02:17:50</t>
+    <t>2026-09-07 11:56:51</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1039,7 +1042,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>15b64f7</t>
+    <t>42941f3</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1355,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1414,6 +1417,7 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1731,7 +1735,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="B1:E32"/>
+  <dimension ref="B1:E33"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1740,19 +1744,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -1796,7 +1800,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>(IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))+C18</f>
+        <f>C18+C19</f>
         <v>921</v>
       </c>
     </row>
@@ -1862,62 +1866,65 @@
         <v>-0.81896551724137934</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="44">
+        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))</f>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="45">
         <f>'Equity Method Value'!C12</f>
         <v>587</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="11">
-        <f>'Comps Analysis'!C27</f>
-        <v>3400</v>
-      </c>
-      <c r="D19" s="7">
-        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="11">
+        <f>'Comps Analysis'!C28</f>
+        <v>2076</v>
+      </c>
+      <c r="D21" s="7">
+        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
         <v>-0.73366606170598914</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="6" t="str">
+    </row>
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="6" t="str">
         <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
         <v>268 - 399</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
@@ -1929,18 +1936,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    </row>
+    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
@@ -1950,6 +1956,11 @@
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1978,25 +1989,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5">
         <v>14724234</v>
@@ -2007,31 +2018,31 @@
     </row>
     <row r="7" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5">
         <v>698080</v>
@@ -2042,7 +2053,7 @@
     </row>
     <row r="12" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5">
         <v>400333</v>
@@ -2053,7 +2064,7 @@
     </row>
     <row r="13" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7">
         <f>C11/C6</f>
@@ -2066,7 +2077,7 @@
     </row>
     <row r="14" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="7">
         <f>C12/C6</f>
@@ -2079,10 +2090,10 @@
     </row>
     <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="7">
         <f>(D6-C6)/C6</f>
@@ -2091,10 +2102,10 @@
     </row>
     <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
         <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="7">
         <f>(D11-C11)/C11</f>
@@ -2103,12 +2114,12 @@
     </row>
     <row r="18" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="5">
         <v>997278</v>
@@ -2119,34 +2130,34 @@
     </row>
     <row r="20" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="5">
         <v>549573</v>
@@ -2157,7 +2168,7 @@
     </row>
     <row r="27" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="5">
         <v>3550768</v>
@@ -2168,7 +2179,7 @@
     </row>
     <row r="28" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="5">
         <f>C27-C26</f>
@@ -2181,7 +2192,7 @@
     </row>
     <row r="30" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2205,12 +2216,12 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2220,7 +2231,7 @@
     </row>
     <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="7">
         <v>3.0939999999999999E-2</v>
@@ -2228,7 +2239,7 @@
     </row>
     <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="7">
         <v>0.25</v>
@@ -2236,7 +2247,7 @@
     </row>
     <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="7">
         <v>2.9700000000000001E-2</v>
@@ -2244,7 +2255,7 @@
     </row>
     <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="12">
         <v>0.94550000000000001</v>
@@ -2252,7 +2263,7 @@
     </row>
     <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="7">
         <v>6.5000000000000002E-2</v>
@@ -2260,7 +2271,7 @@
     </row>
     <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="7">
         <v>0.01</v>
@@ -2268,7 +2279,7 @@
     </row>
     <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7">
         <v>0.01</v>
@@ -2276,7 +2287,7 @@
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="13">
         <v>0.2387</v>
@@ -2284,7 +2295,7 @@
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="7">
         <v>0.01</v>
@@ -2292,7 +2303,7 @@
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="14">
         <v>7</v>
@@ -2300,7 +2311,7 @@
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="15">
         <v>6989912686</v>
@@ -2308,7 +2319,7 @@
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="5">
         <v>3677236</v>
@@ -2316,7 +2327,7 @@
     </row>
     <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="5">
         <v>14823087</v>
@@ -2324,7 +2335,7 @@
     </row>
     <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="7">
         <v>3.0939999999999999E-2</v>
@@ -2332,7 +2343,7 @@
     </row>
     <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -2340,7 +2351,7 @@
     </row>
     <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" s="5">
         <v>14823087</v>
@@ -2348,7 +2359,7 @@
     </row>
     <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -2358,7 +2369,7 @@
     </row>
     <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="16">
         <f>C7+C8*C9+C10</f>
@@ -2367,7 +2378,7 @@
     </row>
     <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="16">
         <f>1/(1+C12)</f>
@@ -2376,7 +2387,7 @@
     </row>
     <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="16">
         <f>C12/(1+C12)</f>
@@ -2385,7 +2396,7 @@
     </row>
     <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="16">
         <f>C23*C24+C11*C25</f>
@@ -2394,10 +2405,10 @@
     </row>
     <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D27" s="6">
         <f>MATCH(C27,B69:B73,0)</f>
@@ -2406,7 +2417,7 @@
     </row>
     <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2416,24 +2427,24 @@
     </row>
     <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="18">
         <f>CHOOSE($D$27,C69,C70,C71,C72,C73)</f>
@@ -2458,7 +2469,7 @@
     </row>
     <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="18">
         <f>CHOOSE($D$27,C76,C77,C78,C79,C80)</f>
@@ -2483,7 +2494,7 @@
     </row>
     <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" s="18">
         <f>CHOOSE($D$27,C83,C84,C85,C86,C87)</f>
@@ -2508,7 +2519,7 @@
     </row>
     <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="5">
         <f>C17*(1+C30)</f>
@@ -2533,7 +2544,7 @@
     </row>
     <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="5">
         <f>C33*C31</f>
@@ -2558,7 +2569,7 @@
     </row>
     <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" s="19">
         <f>C33-C34</f>
@@ -2583,7 +2594,7 @@
     </row>
     <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="7">
         <f>C35/C33</f>
@@ -2608,7 +2619,7 @@
     </row>
     <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="5">
         <f>C33*C32</f>
@@ -2633,7 +2644,7 @@
     </row>
     <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" s="7">
         <f>(C35-C37)/C33</f>
@@ -2658,7 +2669,7 @@
     </row>
     <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="19">
         <f>C35-C37</f>
@@ -2683,7 +2694,7 @@
     </row>
     <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="5">
         <f>MAX(0,C39*C6)</f>
@@ -2708,7 +2719,7 @@
     </row>
     <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="19">
         <f>C39-C40</f>
@@ -2733,7 +2744,7 @@
     </row>
     <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="5">
         <f>C33*C18</f>
@@ -2758,7 +2769,7 @@
     </row>
     <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="5">
         <f>C33*C5</f>
@@ -2783,7 +2794,7 @@
     </row>
     <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="5">
         <f>'NWC Schedule'!D19</f>
@@ -2808,7 +2819,7 @@
     </row>
     <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="20">
         <f>C41+C42-C43-C44</f>
@@ -2833,7 +2844,7 @@
     </row>
     <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="21">
         <f>1/(1+C26)^(C19+0)</f>
@@ -2858,7 +2869,7 @@
     </row>
     <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
@@ -2883,7 +2894,7 @@
     </row>
     <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -2893,7 +2904,7 @@
     </row>
     <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
@@ -2902,7 +2913,7 @@
     </row>
     <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
@@ -2911,7 +2922,7 @@
     </row>
     <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
@@ -2920,7 +2931,7 @@
     </row>
     <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
@@ -2929,7 +2940,7 @@
     </row>
     <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
@@ -2938,7 +2949,7 @@
     </row>
     <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
@@ -2947,7 +2958,7 @@
     </row>
     <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -2957,7 +2968,7 @@
     </row>
     <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="5">
         <f>C50</f>
@@ -2966,7 +2977,7 @@
     </row>
     <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C59" s="5">
         <f>G39+G42</f>
@@ -2975,7 +2986,7 @@
     </row>
     <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
@@ -2984,7 +2995,7 @@
     </row>
     <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
@@ -2993,7 +3004,7 @@
     </row>
     <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
@@ -3002,7 +3013,7 @@
     </row>
     <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
@@ -3011,7 +3022,7 @@
     </row>
     <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
@@ -3020,7 +3031,7 @@
     </row>
     <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
@@ -3030,29 +3041,29 @@
     </row>
     <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C69" s="26">
         <v>0.02</v>
@@ -3072,7 +3083,7 @@
     </row>
     <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" s="26">
         <v>0.04</v>
@@ -3092,7 +3103,7 @@
     </row>
     <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C71" s="26">
         <v>0.02</v>
@@ -3112,7 +3123,7 @@
     </row>
     <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C72" s="26">
         <v>0</v>
@@ -3132,7 +3143,7 @@
     </row>
     <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C73" s="26">
         <v>-0.05</v>
@@ -3152,12 +3163,12 @@
     </row>
     <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="26">
         <v>0.8327</v>
@@ -3177,7 +3188,7 @@
     </row>
     <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C77" s="26">
         <v>0.8327</v>
@@ -3197,7 +3208,7 @@
     </row>
     <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C78" s="26">
         <v>0.8327</v>
@@ -3217,7 +3228,7 @@
     </row>
     <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C79" s="26">
         <v>0.8327</v>
@@ -3237,7 +3248,7 @@
     </row>
     <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C80" s="26">
         <v>0.8327</v>
@@ -3257,12 +3268,12 @@
     </row>
     <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83" s="26">
         <v>0.11890000000000001</v>
@@ -3282,7 +3293,7 @@
     </row>
     <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C84" s="26">
         <v>0.11409999999999999</v>
@@ -3302,7 +3313,7 @@
     </row>
     <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C85" s="26">
         <v>0.11890000000000001</v>
@@ -3322,7 +3333,7 @@
     </row>
     <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C86" s="26">
         <v>0.1237</v>
@@ -3342,7 +3353,7 @@
     </row>
     <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C87" s="26">
         <v>0.12859999999999999</v>
@@ -3386,17 +3397,17 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3408,7 +3419,7 @@
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="15">
         <f>'Executive Summary'!C9</f>
@@ -3417,7 +3428,7 @@
     </row>
     <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="15">
         <f>'DCF Model'!C15</f>
@@ -3426,7 +3437,7 @@
     </row>
     <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="5">
         <f>C6*C7/1000000</f>
@@ -3435,7 +3446,7 @@
     </row>
     <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5">
         <f>'DCF Model'!C16</f>
@@ -3444,7 +3455,7 @@
     </row>
     <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="5">
         <f>C8+C9</f>
@@ -3453,7 +3464,7 @@
     </row>
     <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="16">
         <f>'DCF Model'!C26</f>
@@ -3462,7 +3473,7 @@
     </row>
     <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="16">
         <f>'DCF Model'!C13</f>
@@ -3471,7 +3482,7 @@
     </row>
     <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="16">
         <f>'DCF Model'!C6</f>
@@ -3480,7 +3491,7 @@
     </row>
     <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="27">
         <v>717348</v>
@@ -3488,7 +3499,7 @@
     </row>
     <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="27">
         <v>717348</v>
@@ -3496,7 +3507,7 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="5">
         <f>'DCF Model'!G33</f>
@@ -3505,7 +3516,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="5">
         <f>'DCF Model'!C53</f>
@@ -3514,7 +3525,7 @@
     </row>
     <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="26">
         <v>4.8393968139025287E-2</v>
@@ -3522,7 +3533,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="5">
         <f>C10-C17</f>
@@ -3531,7 +3542,7 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="15">
         <f>IFERROR(ROUND(C19*1000000/C7,0),"N/A")</f>
@@ -3540,7 +3551,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -3552,12 +3563,12 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C24" s="5">
         <f>C10*(C11-C12)</f>
@@ -3566,7 +3577,7 @@
     </row>
     <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C25" s="5">
         <f>IFERROR(C24/(1-C13),"N/A")</f>
@@ -3575,7 +3586,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="14">
         <f>IFERROR(C25/C15,"N/A")</f>
@@ -3584,7 +3595,7 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C27" s="14">
         <f>IFERROR(C25/C14,"N/A")</f>
@@ -3593,7 +3604,7 @@
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="7">
         <f>IFERROR(C25/C16,"N/A")</f>
@@ -3602,7 +3613,7 @@
     </row>
     <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C29" s="5">
         <f>IFERROR(C25/C18,"N/A")</f>
@@ -3611,7 +3622,7 @@
     </row>
     <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -3623,20 +3634,20 @@
     </row>
     <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D36" s="29">
         <f>'DCF Model'!C26-0.02</f>
@@ -3661,12 +3672,12 @@
     </row>
     <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" s="30">
         <v>3</v>
@@ -3694,7 +3705,7 @@
     </row>
     <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" s="30">
         <v>5</v>
@@ -3722,7 +3733,7 @@
     </row>
     <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" s="30">
         <v>7</v>
@@ -3750,7 +3761,7 @@
     </row>
     <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" s="30">
         <v>10</v>
@@ -3778,12 +3789,12 @@
     </row>
     <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" s="30">
         <v>3</v>
@@ -3811,7 +3822,7 @@
     </row>
     <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" s="30">
         <v>5</v>
@@ -3839,7 +3850,7 @@
     </row>
     <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C45" s="30">
         <v>7</v>
@@ -3867,7 +3878,7 @@
     </row>
     <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" s="30">
         <v>10</v>
@@ -3895,7 +3906,7 @@
     </row>
     <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23"/>
@@ -3907,7 +3918,7 @@
     </row>
     <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C48" s="30">
         <v>3</v>
@@ -3935,7 +3946,7 @@
     </row>
     <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" s="30">
         <v>5</v>
@@ -3963,7 +3974,7 @@
     </row>
     <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C50" s="30">
         <v>7</v>
@@ -3991,7 +4002,7 @@
     </row>
     <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C51" s="30">
         <v>10</v>
@@ -4019,7 +4030,7 @@
     </row>
     <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
@@ -4031,7 +4042,7 @@
     </row>
     <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" s="30">
         <v>3</v>
@@ -4059,7 +4070,7 @@
     </row>
     <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C54" s="30">
         <v>5</v>
@@ -4087,7 +4098,7 @@
     </row>
     <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C55" s="30">
         <v>7</v>
@@ -4115,7 +4126,7 @@
     </row>
     <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C56" s="30">
         <v>10</v>
@@ -4143,7 +4154,7 @@
     </row>
     <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -4155,12 +4166,12 @@
     </row>
     <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C60" s="5">
         <f>F49</f>
@@ -4169,13 +4180,13 @@
     </row>
     <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
@@ -4206,7 +4217,7 @@
     </row>
     <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C65" s="5">
         <f>IFERROR($C$60/$C$18,"N/A")</f>
@@ -4245,7 +4256,7 @@
     </row>
     <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -4257,7 +4268,7 @@
     </row>
     <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C70" s="14">
         <f>IFERROR(C10/'Comps Analysis'!G5,"N/A")</f>
@@ -4266,7 +4277,7 @@
     </row>
     <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="14">
         <f>IFERROR(C10/'Comps Analysis'!F5,"N/A")</f>
@@ -4275,7 +4286,7 @@
     </row>
     <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" s="14">
         <f>IFERROR(C10/(C25+'DCF Model'!G42),"N/A")</f>
@@ -4284,7 +4295,7 @@
     </row>
     <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" s="14">
         <f>IFERROR(C10/(C60+'DCF Model'!G42),"N/A")</f>
@@ -4293,7 +4304,7 @@
     </row>
     <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C74" s="14">
         <f>IFERROR('Comps Analysis'!D16,"N/A")</f>
@@ -4302,12 +4313,12 @@
     </row>
     <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C77" s="23"/>
       <c r="D77" s="23"/>
@@ -4350,35 +4361,35 @@
   <sheetData>
     <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" s="34">
         <f>C18/C9</f>
@@ -4407,53 +4418,53 @@
     </row>
     <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -4464,7 +4475,7 @@
     </row>
     <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="36">
         <v>14823087</v>
@@ -4492,30 +4503,30 @@
     </row>
     <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4526,122 +4537,122 @@
     </row>
     <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -4652,7 +4663,7 @@
     </row>
     <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="20">
         <v>1544795</v>
@@ -4680,10 +4691,10 @@
     </row>
     <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="24">
         <f>D18-C18</f>
@@ -4708,7 +4719,7 @@
     </row>
     <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -4719,29 +4730,29 @@
     </row>
     <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="26">
         <v>0.2127</v>
@@ -4761,7 +4772,7 @@
     </row>
     <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="26">
         <v>0.2127</v>
@@ -4781,7 +4792,7 @@
     </row>
     <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="26">
         <v>0.2127</v>
@@ -4801,7 +4812,7 @@
     </row>
     <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D28" s="26">
         <v>0.2127</v>
@@ -4821,7 +4832,7 @@
     </row>
     <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" s="26">
         <v>0.2127</v>
@@ -4862,12 +4873,12 @@
   <sheetData>
     <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
@@ -4878,54 +4889,54 @@
         <v>5</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="38">
         <f>'Executive Summary'!C9*C23/1000000</f>
@@ -4977,10 +4988,10 @@
     </row>
     <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" s="38">
         <v>8253340</v>
@@ -5030,10 +5041,10 @@
     </row>
     <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" s="38">
         <v>14224791</v>
@@ -5083,10 +5094,10 @@
     </row>
     <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D8" s="38">
         <v>8603005</v>
@@ -5136,10 +5147,10 @@
     </row>
     <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" s="38">
         <v>17948666</v>
@@ -5189,12 +5200,12 @@
     </row>
     <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D15" s="39">
         <f t="shared" ref="D15:I15" si="0">PERCENTILE(J6:J9,0.25)</f>
@@ -5223,7 +5234,7 @@
     </row>
     <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D16" s="39">
         <f t="shared" ref="D16:I16" si="1">MEDIAN(J6:J9)</f>
@@ -5252,7 +5263,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D17" s="39">
         <f t="shared" ref="D17:I17" si="2">PERCENTILE(J6:J9,0.75)</f>
@@ -5281,7 +5292,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -5293,12 +5304,12 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C21" s="5">
         <v>1176044</v>
@@ -5306,7 +5317,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="5">
         <v>900283</v>
@@ -5314,7 +5325,7 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C23" s="15">
         <v>6989912686</v>
@@ -5322,7 +5333,7 @@
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="5">
         <v>3677236</v>
@@ -5330,12 +5341,12 @@
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C27" s="24">
         <f>ROUND((C21*D16-C24)*1000000/C23,0)</f>
@@ -5344,7 +5355,7 @@
     </row>
     <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C28" s="24">
         <f>ROUND(C22*F16*1000000/C23,0)</f>
@@ -5372,26 +5383,26 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C3" s="16">
         <f>'DCF Model'!C26</f>
         <v>8.3591265035924761E-2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F3" s="16">
         <f>'DCF Model'!C13</f>
         <v>0.01</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I3" s="14">
         <f>'DCF Model'!C14</f>
@@ -5400,12 +5411,12 @@
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C6" s="42">
         <f>$F$3-0.0075</f>
@@ -5676,12 +5687,12 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C17" s="43">
         <f>$I$3-3</f>
@@ -5951,16 +5962,16 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="55" t="s">
-        <v>231</v>
-      </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
+      <c r="B26" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5989,165 +6000,165 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F5" t="s">
         <v>241</v>
       </c>
-      <c r="E5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F5" t="s">
-        <v>240</v>
-      </c>
       <c r="G5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -6155,319 +6166,319 @@
     </row>
     <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C35" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C40" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C44" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C45" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C54" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C57" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C59" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C60" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C64">
         <v>4104790</v>
@@ -6475,7 +6486,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6483,10 +6494,10 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C66" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -6510,75 +6521,75 @@
   <sheetData>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="45" t="s">
-        <v>343</v>
+      <c r="B3" s="46" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="C6" s="47">
+      <c r="B6" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="48">
         <v>4104790</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="46" t="s">
-        <v>346</v>
-      </c>
-      <c r="C7" s="48">
+      <c r="B7" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="49">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="C8" s="50">
+      <c r="B8" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="51">
         <f>C6*C7</f>
         <v>4104790</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="51" t="s">
-        <v>348</v>
+      <c r="B9" s="52" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="C11" s="52">
+      <c r="B11" s="47" t="s">
+        <v>350</v>
+      </c>
+      <c r="C11" s="53">
         <f>'DCF Model'!C15</f>
         <v>6989912686</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B12" s="49" t="s">
-        <v>350</v>
-      </c>
-      <c r="C12" s="50">
+      <c r="B12" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="C12" s="51">
         <f>ROUND(C8/C11*1000000,0)</f>
         <v>587</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
-        <v>351</v>
+      <c r="B14" s="46" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
-        <v>352</v>
+      <c r="B15" s="46" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/models/8001_DCF_Model_20260906.xlsx
+++ b/models/8001_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54306A9-3AB2-4E51-B910-4BDCBF2CF4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5C0C0E-0872-4AF4-BBE0-ED8BD159FA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="355">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Current Price</t>
   </si>
   <si>
-    <t>Target Price (コアDCF + 持分法投資価値)</t>
+    <t>Target Price (コアDCF[フロア適用] + 持分法投資価値)</t>
   </si>
   <si>
     <t>Recommendation</t>
@@ -87,22 +87,22 @@
     <t>DCF - Exit Multiple</t>
   </si>
   <si>
-    <t>コアDCF 1株値（フロア規則: 負または不成立なら 0）</t>
+    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型F: EV倍率は持分法混在で歪むため不使用）</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Comps - PER Median [参考・Target不算入]</t>
+  </si>
+  <si>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'book_value'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
+  </si>
+  <si>
+    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>持分法投資価値 [1株・別途加算]</t>
-  </si>
-  <si>
-    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型F: EV倍率は持分法混在で歪むため不使用）</t>
-  </si>
-  <si>
-    <t>Comps - PER Median [参考・Target不算入]</t>
-  </si>
-  <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'book_value'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
-  </si>
-  <si>
-    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>Key Investment Thesis</t>
@@ -763,7 +763,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 11:56, template rev 42941f3</t>
+    <t>Generated by pipeline on 2026-09-07 13:04, template rev b0a6ac9</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -973,7 +973,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 11:56:51</t>
+    <t>2026-09-07 13:04:04</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1042,7 +1042,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>42941f3</t>
+    <t>b0a6ac9</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1058,6 +1058,9 @@
   </si>
   <si>
     <t>equity_method_multiple</t>
+  </si>
+  <si>
+    <t>equity_method_fair_value_based</t>
   </si>
   <si>
     <t>equity_method_basis</t>
@@ -1358,7 +1361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1417,7 +1420,6 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1735,7 +1737,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="B1:E33"/>
+  <dimension ref="B1:E31"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1744,19 +1746,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
     </row>
     <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -1800,7 +1802,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>C18+C19</f>
+        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22</f>
         <v>921</v>
       </c>
     </row>
@@ -1866,100 +1868,98 @@
         <v>-0.81896551724137934</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="44">
-        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))</f>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="45">
+      <c r="D18" s="7" t="str">
+        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="11">
+        <f>'Comps Analysis'!C28</f>
+        <v>2076</v>
+      </c>
+      <c r="D19" s="7">
+        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
+        <v>-5.8076225045372049E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
+        <v>268 - 399</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="44">
         <f>'Equity Method Value'!C12</f>
         <v>587</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="11">
-        <f>'Comps Analysis'!C28</f>
-        <v>2076</v>
-      </c>
-      <c r="D21" s="7">
-        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
-        <v>-0.73366606170598914</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
-        <v>268 - 399</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="B23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B30" s="8" t="s">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5962,16 +5962,16 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5987,7 +5987,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G66"/>
+  <dimension ref="B2:G67"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -6497,7 +6497,15 @@
         <v>341</v>
       </c>
       <c r="C66" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
         <v>342</v>
+      </c>
+      <c r="C67" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -6521,75 +6529,75 @@
   <sheetData>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>344</v>
+      <c r="B3" s="45" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
-        <v>346</v>
-      </c>
-      <c r="C6" s="48">
+      <c r="B6" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="47">
         <v>4104790</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="49">
+      <c r="B7" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="48">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="51">
+      <c r="B8" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="50">
         <f>C6*C7</f>
         <v>4104790</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="52" t="s">
-        <v>349</v>
+      <c r="B9" s="51" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C11" s="53">
+      <c r="B11" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="C11" s="52">
         <f>'DCF Model'!C15</f>
         <v>6989912686</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B12" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="C12" s="51">
+      <c r="B12" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="50">
         <f>ROUND(C8/C11*1000000,0)</f>
         <v>587</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="46" t="s">
-        <v>352</v>
+      <c r="B14" s="45" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B15" s="46" t="s">
-        <v>353</v>
+      <c r="B15" s="45" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
